--- a/0 zombie num/masks_cal.xlsx
+++ b/0 zombie num/masks_cal.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14955" windowHeight="9930"/>
+    <workbookView windowWidth="18570" windowHeight="13365"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
@@ -1322,7 +1322,9 @@
       <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1">
         <v>1</v>
@@ -1353,9 +1355,7 @@
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2">
         <v>1</v>
       </c>
@@ -1454,9 +1454,7 @@
       <c r="B8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3">
         <v>1</v>
       </c>
@@ -1523,7 +1521,9 @@
       <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="F12" s="2">
         <v>1</v>
@@ -1722,7 +1722,7 @@
     <row r="21" spans="1:12">
       <c r="C21" s="7">
         <f>SUM(C2+2*C3+4*C4+8*C5+16*C6+32*C7+64*C8+128*C9+256*C10+512*C11+1024*C12+2048*C13+4096*C14+8192*C15+16384*C16+32768*C17+65536*C18+131072*C19+262144*C20)</f>
-        <v>395626</v>
+        <v>396585</v>
       </c>
       <c r="D21" s="7">
         <f>SUM(D2+2*D3+4*D4+8*D5+16*D6+32*D7+64*D8+128*D9+256*D10+512*D11+1024*D12+2048*D13+4096*D14+8192*D15+16384*D16+32768*D17+65536*D18+131072*D19+262144*D20)</f>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C23" s="7">
         <f t="array" ref="C23">SUM(A2:A20*C2:C20)+401-A16*C16</f>
-        <v>12901</v>
+        <v>11901</v>
       </c>
     </row>
   </sheetData>
